--- a/PCB/solar-glow-drh-v3 0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3 0-BOM.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="10" min="1" max="1"/>
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="H2" s="16" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="I2" s="16" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
@@ -558,7 +558,7 @@
       </c>
       <c r="K2" s="15" t="inlineStr">
         <is>
-          <t>VQFN land has an exposed pad → EP to GND. /STX confirmed = VQFN-28 (4×4).</t>
+          <t>VQFN land has an exposed pad → EP to GND. /STX confirmed = VQFN-28 (4×4). DK verified 2026-07-02: Active, tube, $1.17 @ 1, VQFN28 (4x4) confirmed on the DK listing.</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="M2" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>150-AVR64DD28-I/STX-ND</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="K3" s="15" t="inlineStr">
         <is>
-          <t>TF = the 1.2 mm 'thin' variant; electrically identical to the 1.8 mm SM141K06L. Same 42×23 land.</t>
+          <t>TF = the 1.2 mm 'thin' variant; electrically identical to the 1.8 mm SM141K06L. Same 42×23 land. DK verified 2026-07-02. TF = Gen3 Thin: ANYSOLAR PCN ASL2022-001 maps SM141K06L (Standard) -&gt; SM141K06TF (Thin) - the citation for the pending sch value fix.</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="M3" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>2994-SM141K06TF-ND</t>
         </is>
       </c>
     </row>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.125</v>
+        <v>0.37</v>
       </c>
       <c r="I4" s="16" t="n">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="J4" s="13" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
-          <t>Low-Vf for the ~4 V solar; one per panel so a half-shadow can't back-feed.</t>
+          <t>Low-Vf for the ~4 V solar; one per panel so a half-shadow can't back-feed. DK P/N re-verified verbatim 2026-07-02 ($0.37 @ 1). Non-G MMSD301T1 is obsolete (Rochester stock only) - keep the G.</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="K5" s="15" t="inlineStr">
         <is>
-          <t>⚠ DOMINANT COST. Solder to the under-body flat pads (asymmetric P/N widths = polarity key), NOT the end tabs. Confirm live price.</t>
+          <t>⚠ DOMINANT COST. Solder to the under-body flat pads (asymmetric P/N widths = polarity key), NOT the end tabs. Confirm live price. DK product page verified 2026-07-02 (1 F, 2.75 V, SCPC). DK part number string not captured - order by MPN.</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="M5" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>ALD810025-2.pdf is the combined 810025/910025 datasheet — it covers this dual. SALI = industrial temp.</t>
+          <t>ALD810025-2.pdf is the combined 810025/910025 datasheet — it covers this dual. SALI = industrial temp. DK page verified 2026-07-02 (Active, SOIC-8; DK-hosted combined datasheet lists ALD910025SALI in the ordering table). The -ND number shown left is the expected form but was NOT observed verbatim - confirm at cart.</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>ALD810025-2.pdf</t>
+          <t>ALD810025-2.pdf (combined ALD8100xx/ALD9100xx doc)</t>
         </is>
       </c>
       <c r="M6" s="13" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="H7" s="16" t="n">
-        <v>0.273</v>
+        <v>0.43</v>
       </c>
       <c r="I7" s="16" t="n">
-        <v>1.092</v>
+        <v>1.72</v>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="K7" s="15" t="inlineStr">
         <is>
-          <t>Reverse-mount; light path runs through the all-layer keepout window.</t>
+          <t>Reverse-mount; light path runs through the all-layer keepout window. Fully verified 2026-07-02: DK lists the full code; ams-OSRAM packing doc maps it to Q65110A9267 = the REVERSE-mount bin per the LA P47F datasheet; DK CT number confirmed verbatim; 11.3k in stock; $0.43 @ 1 / $0.294 @ 10.</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-07150RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="M9" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-07220RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="M10" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="M11" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>GRM155R71C103KA01D-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="H12" s="16" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="I12" s="16" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>CS→VS (I²C mode), SDO/SA0→GND (addr 0x18). SCL=PC3, SDA=PC2.</t>
+          <t>CS→VS (I²C mode), SDO/SA0→GND (addr 0x18). SCL=PC3, SDA=PC2. DK verified 2026-07-02: 12-LGA (2x2), $1.79 @ 1, 40k stock.</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="M12" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>497-14851-2-ND (T&amp;R form observed; pick CT at cart)</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="M13" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-074K7L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>B grade (tighter) for a predictable clamp. tlv431a-3.pdf is TI's combined A/B datasheet.</t>
+          <t>B grade (tighter) for a predictable clamp. tlv431a-3.pdf is TI's combined A/B datasheet. DK verified 2026-07-02 (SOT-23-3, Active in TI ordering table). Note: C temp grade = 0-70 C, fine for card duty.</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="M14" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>296-17569-1-ND</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>SOT / WDFN</t>
+          <t>WDFN 2×2 (case 515AA)</t>
         </is>
       </c>
       <c r="F15" s="13" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Emitter=VS, collector=GND, base=CLBASE.</t>
+          <t>Emitter=VS, collector=GND, base=CLBASE. AVAILABILITY FLAG 2026-07-02: MPN is real (onsemi BCP53M/D: WDFNW3 2x2, case 515AA, code 3P, 3000/T&amp;R) but no DigiKey or Mouser listing surfaced. Do NOT accept DK fuzzy-match BCP5316TA (Diodes SOT-223 - wrong package). Same-case alternates: NSVBCP5316MTWG (AEC twin) or BCP5310MTWG (hFE 63-160 bin; base-drive margin OK). Check DK/Mouser/Arrow at order time.</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>(not listed at DigiKey — see note)</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="M16" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-071M8L-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M17" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-071ML-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="M18" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0402FR-071KL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1554,8 +1554,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="H19" s="16" t="n"/>
-      <c r="I19" s="16" t="n"/>
+      <c r="H19" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1563,7 +1567,7 @@
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC]</t>
+          <t xml:space="preserve"> [v3.0: 0402 to match board land; price TBC] DK verified 2026-07-02 via this MPN: 490-3261-1-ND, $0.10 @ 1 CT; C2/C3/C6/C7/C8 are the same line item.</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
@@ -1573,7 +1577,7 @@
       </c>
       <c r="M19" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
@@ -1611,8 +1615,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="H20" s="16" t="n"/>
-      <c r="I20" s="16" t="n"/>
+      <c r="H20" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1630,7 +1638,7 @@
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1695,7 @@
       </c>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>GRM155R61A105KE15D-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -1725,8 +1733,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="H22" s="16" t="n"/>
-      <c r="I22" s="16" t="n"/>
+      <c r="H22" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1744,7 +1756,7 @@
       </c>
       <c r="M22" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
@@ -1782,8 +1794,12 @@
           <t>GRM155R71C104KA88D</t>
         </is>
       </c>
-      <c r="H23" s="16" t="n"/>
-      <c r="I23" s="16" t="n"/>
+      <c r="H23" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -1801,7 +1817,7 @@
       </c>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1874,7 @@
       </c>
       <c r="M24" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>RC0805JR-070RL-ND (format-derived — confirm at cart)</t>
         </is>
       </c>
     </row>
@@ -2107,163 +2123,167 @@
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="11">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>MH1–MH4</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>M2 mounting holes (grounded), board corners</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>2.2 mm plated</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>(no part — drill)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="n">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>JP1</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Bench pad strip — GND / VS / SCL / SDA probe pads (bench power injection + I²C tap)</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>4× bare SMD pads</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>1.7 mm sq, 2.54 mm pitch, B side</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>(bare pads — no component)</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="16" t="n">
+      <c r="I29" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K29" s="15" t="inlineStr">
-        <is>
-          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M29" s="13" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>v3.0 addition at (48.4, 14.54–22.16). Nothing to buy or place — mark DNP in the CPL. Pinout + bench ritual in solar-glow-drh-v2-hardware.md.</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30" ht="23.25" customHeight="1" s="11">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="n">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="inlineStr">
-        <is>
-          <t>NXP</t>
-        </is>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>NT3H2211W0FHKH</t>
-        </is>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K30" s="15" t="inlineStr">
-        <is>
-          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x18). VCC→VS; VOUT pin 7 unconnected. Confirm live price.</t>
-        </is>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>NT3H2111_2211.pdf</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr">
-        <is>
-          <t>(by MPN)</t>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>VIN test pad (pre-D1 solar node) — charge test / panel emulation</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>1× bare SMD pad</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>1.7 mm sq, B side</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>(bare pad — no component)</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>v3.0 addition at (48.4, 12.0). Mark DNP in the CPL.</t>
+        </is>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="31" ht="23.25" customHeight="1" s="11">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>MH1–MH4</t>
         </is>
       </c>
       <c r="B31" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>NFC tag (U5) VCC decoupling</t>
+          <t>M2 mounting holes (grounded), board corners</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>100 nF, X7R, 16 V</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>2.2 mm plated</t>
         </is>
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>GRM155R71C104KA88D</t>
-        </is>
-      </c>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="16" t="n"/>
+          <t>(no part — drill)</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -2271,24 +2291,24 @@
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>Ties a metal back-plate to GND if enclosed; user-supplied M2 hardware.</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
         <is>
-          <t>(Murata GRM155 family)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="11">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B32" s="14" t="n">
@@ -2296,60 +2316,60 @@
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
+          <t>NFC tag — NTAG I²C plus 2K; phone reads/writes EEPROM, FD signals field to MCU</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>DNP (NP0/C0G land)</t>
+          <t>NTAG I²C plus, 2 KB, I²C 0x55</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>0402 (NP0/C0G land)</t>
+          <t>XQFN8 (SOT902-3, 1.6×1.6×0.5 mm)</t>
         </is>
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NXP</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>(DNP — not ordered)</t>
+          <t>NT3H2211W0FHKH</t>
         </is>
       </c>
       <c r="H32" s="16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="I32" s="16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>DNP</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>v2.2 NFC. Do-not-populate; optional external trim only if the coil needs retuning. [v3.0: 0402 land; bench-trim with an NP0 range ~47–150 pF, shell fitted]</t>
+          <t>v2.2 NFC addition. XQFN8 = SOT902-3 (datasheet Table 1). I²C 0x55 (no clash w/ accel 0x18). VCC→VS; VOUT pin 7 unconnected. Confirm live price. DK page verified 2026-07-02 (XFQFN8 exposed pad, $1.38 @ 1); Mouser cross: 771-NT3H2211W0FHKH, 9k stock.</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NT3H2111_2211.pdf</t>
         </is>
       </c>
       <c r="M32" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(DK page verified — order by MPN)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="11">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="B33" s="14" t="n">
@@ -2357,12 +2377,12 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>NFC FD pull-up — open-drain FD (U5 pin 4) → PA6</t>
+          <t>NFC tag (U5) VCC decoupling</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>10 kΩ, ±1%</t>
+          <t>100 nF, X7R, 16 V</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -2372,16 +2392,20 @@
       </c>
       <c r="F33" s="13" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>RC0402FR-0710KL</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="16" t="n"/>
+          <t>GRM155R71C104KA88D</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>0.1</v>
+      </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
           <t>LOCKED</t>
@@ -2389,85 +2413,85 @@
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC]</t>
+          <t>v2.2 NFC addition. Same part as C1/C2/C3/C6/C7. [v3.0: 0402 to match board land; price TBC]</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(Murata GRM155 family)</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr">
         <is>
-          <t>(by MPN)</t>
+          <t>490-3261-1-ND</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="11">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>U6</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="n">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>High-side load switch</t>
-        </is>
-      </c>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>SOT-23-6 (DBV)</t>
-        </is>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>Texas Instruments</t>
-        </is>
-      </c>
-      <c r="G34" s="10" t="inlineStr">
-        <is>
-          <t>TPS22918DBVR</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I34" s="10" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J34" s="10" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K34" s="10" t="inlineStr">
-        <is>
-          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/tps22918.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
-        </is>
-      </c>
-      <c r="L34" s="10" t="inlineStr">
-        <is>
-          <t>datasheets/tps22918.pdf</t>
-        </is>
-      </c>
-      <c r="M34" s="10" t="inlineStr">
-        <is>
-          <t>(by MPN)</t>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>NFC antenna trim — DNP (U5's internal 50 pF tunes the coil)</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>DNP (NP0/C0G land)</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>0402 (NP0/C0G land)</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>(DNP — not ordered)</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="K34" s="15" t="inlineStr">
+        <is>
+          <t>v2.2 NFC. Do-not-populate; optional external trim only if the coil needs retuning. [v3.0: 0402 land; bench-trim with an NP0 range ~47–150 pF, shell fitted]</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="35" ht="23.85" customHeight="1" s="11">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
@@ -2475,73 +2499,259 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
+          <t>NFC antenna — PCB coil (LA/LB routed copper, F+B)</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>2.76 µH design value</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>PCB copper — no package</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>(no part — PCB feature)</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>NO PART</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>Sch-only symbol, no footprint. Inductance set by copper geometry; C9 land reserved for bench trim against it. Nothing to order or place.</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="11">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>NFC FD pull-up — open-drain FD (U5 pin 4) → PA6</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>10 kΩ, ±1%</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>0402</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="inlineStr">
+        <is>
+          <t>Yageo</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>RC0402FR-0710KL</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="n"/>
+      <c r="I36" s="16" t="n"/>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K36" s="15" t="inlineStr">
+        <is>
+          <t>v2.2 NFC addition. Pulls open-drain FD up to VS. [v3.0: 0402 to match board land; price TBC]</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="inlineStr">
+        <is>
+          <t>RC0402FR-0710KL-ND (format-derived — confirm at cart)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>U6</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>NFC VNFC load switch — power-gates U5 VCC from PA7 (NFC_EN)</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>High-side load switch</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>SOT-23-6 (DBV)</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Texas Instruments</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>TPS22918DBVR</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I37" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>v3.0 addition. VIN=VS, VOUT=VNFC, ON=NFC_EN, QOD strapped to VOUT (internal RPD ~25 ohm discharge), CT floating (sanctioned per DS). Pin map VERIFIED against TI SLVSD76C (TPS22918 Rev C, repo datasheets/tps22918.pdf; the -Q1 doc SLVSCZ8B matches identically) 2026-07-02 -- check caught a real board defect (VIN/VOUT + GND/QOD transposed on the symbol); fixed on the board same day. $0.55 @ qty 1 (DigiKey, 2026-07-02). ISD 0.5 uA typ / 3.5 uA max standing draw on VS when off.</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr">
+        <is>
+          <t>tps22918.pdf</t>
+        </is>
+      </c>
+      <c r="M37" s="10" t="inlineStr">
+        <is>
+          <t>(DK page verified — order by MPN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="11">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>100 kΩ, ±1%</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>0402</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Yageo</t>
         </is>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>RC0402FR-07100KL</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr">
-        <is>
-          <t>LOCKED</t>
-        </is>
-      </c>
-      <c r="K35" s="10" t="inlineStr">
-        <is>
-          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). Price TBC.</t>
-        </is>
-      </c>
-      <c r="L35" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="10" t="inlineStr">
-        <is>
-          <t>(by MPN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="11">
-      <c r="G36" s="17" t="inlineStr">
+      <c r="H38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>RC0402FR-07100KL-ND</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Parts subtotal (per board, indicative)</t>
         </is>
       </c>
-      <c r="I36" s="18">
-        <f>SUM(I2:I35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38" ht="15" customHeight="1" s="11">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.</t>
+      <c r="I39" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Sum of the 28 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A38:M38"/>
-  </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/PCB/solar-glow-drh-v3 0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3 0-BOM.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="10" min="1" max="1"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="K6" s="15" t="inlineStr">
         <is>
-          <t>ALD810025-2.pdf is the combined 810025/910025 datasheet — it covers this dual. SALI = industrial temp. DK page verified 2026-07-02 (Active, SOIC-8; DK-hosted combined datasheet lists ALD910025SALI in the ordering table). The -ND number shown left is the expected form but was NOT observed verbatim - confirm at cart.</t>
+          <t>DK page fetched 2026-07-02 (Devin-supplied URL): Active, tube, $7.68 @ 1 — but only 43 in stock and 8-wk mfr lead once depleted, so buy a spare. Page: "MOSFET DUAL SAB 2.5V", 8-SOIC 3.90 mm, dual N-ch = one package balances the 2-series stack. DK datasheet link = aldinc.com ALD810025.pdf (the combined ALD8100xx/9100xx doc = repo file). I-suffix = industrial temp; sch value fixed to SALI and committed.</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="H15" s="16" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="I15" s="16" t="n">
-        <v>0.45</v>
+        <v>0.79</v>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="K15" s="15" t="inlineStr">
         <is>
-          <t>Emitter=VS, collector=GND, base=CLBASE. AVAILABILITY FLAG 2026-07-02: MPN is real (onsemi BCP53M/D: WDFNW3 2x2, case 515AA, code 3P, 3000/T&amp;R) but no DigiKey or Mouser listing surfaced. Do NOT accept DK fuzzy-match BCP5316TA (Diodes SOT-223 - wrong package). Same-case alternates: NSVBCP5316MTWG (AEC twin) or BCP5310MTWG (hFE 63-160 bin; base-drive margin OK). Check DK/Mouser/Arrow at order time.</t>
+          <t>DK page fetched 2026-07-02 (Devin-supplied URL): Active, 2,961 in stock, bulk, $0.79 @ 1 / $0.489 @ 10. Page confirms 3-WDFNW (2×2) WETTABLE FLANK = board land (onsemi case 515AA) and hFE bin 100 @ 150 mA; DK datasheet link = repo BCP53M-D.PDF. Mfr restock lead 32 wk — buy spares. Fallback alternates if ever dry: NSVBCP5316MTWG (auto twin), BCP5310MTWG (lower-bin, same case).</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="M15" s="13" t="inlineStr">
         <is>
-          <t>(not listed at DigiKey — see note)</t>
+          <t>488-BCP5316MTWG-ND</t>
         </is>
       </c>
     </row>
@@ -2673,15 +2673,15 @@
           <t>R14</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>NFC_EN pulldown — holds U6 OFF while PA7 tristates (UPDI / reset / brown-out)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>100 kΩ, ±1%</t>
         </is>
@@ -2691,61 +2691,414 @@
           <t>0402</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>Yageo</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>RC0402FR-07100KL</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>LOCKED</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>v3.0 addition, placed with the R14 board patch at (4.39, 29.4). DK verified 2026-07-02: RC0402FR-07100KL-ND (CT, Active, $0.10 @ 1); legacy 311-100KLRCT-ND also live.</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
         <is>
           <t>RC0402FR-07100KL-ND</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Parts subtotal (per board, indicative)</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>92.91</v>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>— AUXILIARY / OFF-BOARD PURCHASABLES — needed to program, assemble, and enclose the card; never placed on the PCB, excluded from the CPL and assembly BOM —</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>PRG1</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>UPDI programmer — USB-C serial-UPDI with built-in loop-back R and switchable 3V/5V supply (use 3V ONLY; powers the card while flashing)</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Adafruit UPDI Friend</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>26.4×17.8 mm board + JST-SH lead</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Adafruit</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>DK page verified 2026-07-02 ($6.95; the exact DK URL is cited in firmware/README §3). Standard (non-HV) variant is the right one — HV (5893) only if UPDI is ever fused off. Adafruit direct shows out-of-stock and routes to DigiKey.</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>(guide linked in firmware/README)</t>
+        </is>
+      </c>
+      <c r="M40" s="10" t="inlineStr">
+        <is>
+          <t>(DK page verified — order by MPN 5879, Adafruit Industries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>CBL1</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>TC2030 pogo cable — mates TC1 hands-free (4 legs latch the Ø2.37 holes, 3 locating pins, spring contacts on the pads)</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>TC2030-MCP (legged, RJ12 end)</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>6-ft cable, 6P6C modular plug</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Tag-Connect</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>TC2030-MCP</t>
+        </is>
+      </c>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>DK page verified 2026-07-02; DK-hosted datasheet confirms the LEGGED version (matches the board holes — do NOT buy -NL). RJ12 end plugs PICkit 4/5 / MPLAB SNAP directly. For the UPDI-Friend jumper-wire path, sibling TC2030-IDC (same legged nails, 6-pin 0.1″ IDC, $43.71 observed) is the friendlier termination — either works; J1 is the zero-cost fallback.</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>TC2030-MCP.pdf</t>
+        </is>
+      </c>
+      <c r="M41" s="10" t="inlineStr">
+        <is>
+          <t>(DK page verified — order by MPN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>HW1</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Enclosure screws — clamp the board into the tapped Ti bosses (~2.2 mm engagement); brass ties shell to board GND</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>M2 × 3 mm slotted cheese head, brass, DIN 84</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>head ⌀3.8 × 1.4 mm</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>DIN 84 M2×3 brass</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Spec per enclosure/README §7 (customer-supplied). Amazon example verified 2026-07-02: “M2 x 3mm Brass Slotted Cheese Head, 100-Piece”, ASIN B06WLN47XV — listing states DIN84, head ⌀3.8/1.4 mm, matching the callout. Precision alt: Accu SFE-M2-3 series (brass).</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>docs/screw-m2x3-cheese.png</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>ENC1</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Machined titanium back-shell — Ti-max (or the progwindow variant for in-enclosure re-flash)</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Ti-6Al-4V, 3.55 mm stack</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>CNC from enclosure/ STEP</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>(PCBWay CNC or equiv.)</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>(order from enclosure/*.step)</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>Order per enclosure/README (order parameters, callouts C1–C4, notes 1–10). Two variants committed; pick ONE. Fasteners and PCB are separate (README note).</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>enclosure/README.md</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>INS1</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Kapton isolation blanket — die-cut ~0.05 mm polyimide layer between board back and the grounded Ti interior</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>~0.05 mm polyimide, die-cut to board outline</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>sheet / die-cut</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>(polyimide film, 0.05 mm)</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>Standing part of the enclosed build (design-notes §enclosure + mechanical.md): blanket isolation so nothing on the back can short to the shell. Cut to the 50.8 × 88.9 outline with corner-hole clearances.</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>RFL1</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Adhesive reflector strip — sits in the laser-marked 20.9 × 6.2 mm frame on the cavity floor, bounces LED light back through the monogram</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>~21 × 6 mm white/specular film, adhesive-backed</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>die-cut strip</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>(generic)</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>(reflective film, adhesive)</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>Located by the enclosure’s laser-marked registration frame (enclosure/README §9). Exact film spec TBD at bench (white vs specular — trial both against glow evenness).</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Sum of the 28 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="19" t="inlineStr">
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>

--- a/PCB/solar-glow-drh-v3 0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3 0-BOM.xlsx
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>v2.2 NFC. Do-not-populate; optional external trim only if the coil needs retuning. [v3.0: 0402 land; bench-trim with an NP0 range ~47–150 pF, shell fitted]</t>
+          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D.</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">

--- a/PCB/solar-glow-drh-v3 0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3 0-BOM.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" style="10" min="1" max="1"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D.</t>
+          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): a 0.3 mm µ′~100-150 sheet against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -3082,23 +3082,78 @@
       </c>
     </row>
     <row r="46">
-      <c r="G46" s="10" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FER1</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>WE-FSFS material 364 (13.56 MHz grade), 0.3 mm, cut to 12.2 × 25.8 mm</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Würth Elektronik</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>364006</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>AUX</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Observed at RS 2026-07-03 (364006 = 60×60×0.3 WE-FSFS); DigiKey carries the WE-FSFS line — confirm size/thickness variant at cart (~$15-20 sheet class at RS/Farnell). Material 364 is Würth’s 13.56 MHz redirection grade per app note ANP022 (metal detune elimination described verbatim). Laser-scored 2×2 mm grid cuts to size; PET face to the board, PSA face into the brace pocket (brace stays removable, ferrite captive). Non-conductive as supplied. Alternates: MARUWA FSF131/FSF151 (µ′ 130–150 @13.56), Fair-Rite flexible sheets.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>ANP022 (Würth app note)</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>(confirm at cart — order by MPN 364006)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="G47" s="10" t="inlineStr">
         <is>
           <t>On-board parts subtotal (per board, indicative — aux items below excluded)</t>
         </is>
       </c>
-      <c r="I46" s="10" t="n">
+      <c r="I47" s="10" t="n">
         <v>93.25</v>
       </c>
-      <c r="K46" s="10" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Sum of the 28 priced Ext$ cells only — several converted lines remain unpriced pending quotes; see footnote.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="19" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>*≈$/ea is indicative (qty 1–10, USD, ~2026) for a board-cost sanity check only — confirm live pricing at order. Supercaps + solar cells dominate. Mounting holes, SW2 and the SBn bridges carry no ordered part; the NFC coil is PCB-etched copper (no ordered part); headers (J1) unpopulated. Lineage: the old solar-glow-drh-BOM.xlsx is the v0-prototype record; v2.2 added the NFC tag (U5) + C8/C9/R13. v3.0 adds U6 (TPS22918 VNFC load switch) + R14 (100 k NFC_EN pulldown) and converts every passive except SJ1 to 0402 to match the board lands — converted/added lines have prices blanked pending a fresh quote.  |  DigiKey P/Ns and MPN status verified against live DigiKey listings 2026-07-02; per-row notes carry the evidence level (verbatim-observed vs format-derived vs page-verified).</t>
         </is>

--- a/PCB/solar-glow-drh-v3 0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3 0-BOM.xlsx
@@ -2474,7 +2474,7 @@
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): a 0.3 mm µ′~100-150 sheet against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
+          <t>NFC tank trim across LA-LB, parallel with the chip Ci (44-56 pF, typ 50). Computed 2026-07-02 from the committed coil copper (partial-inductance sum over all 73 loop segments, exact parallel-pair mutuals): L0 = 0.98 uH bare -&gt; C_total 140 pF -&gt; C9 ~90 pF typ. START 82-100 pF C0G 0402 and bench-trim to 13.56 MHz. Ti shell detunes: perfect-plane image at the 1.85 mm cavity standoff bounds L_eff at 0.68 uH -&gt; C9 up to ~150 pF enclosed (lossy Ti lands between; Q drops regardless). Stock a C0G ladder: 68/82/100/120/150 pF. NOTE: sch L1 value 2.76 uH is a stale pre-rebuild estimate -&gt; fix to ~1.0 uH at next sch touch. Ladder MPNs (Murata GRM1555C1H family = 0402 C0G 50V, format-derived, confirm at cart): 68p GRM1555C1H680JA01D / 82p GRM1555C1H820JA01D / 100p GRM1555C1H101JA01D / 120p GRM1555C1H121JA01D / 150p GRM1555C1H151JA01D. FERRITE SCENARIO (FER1 adopted): the 364006 sheet (0.38 mm stack, µ′~100-150 class ferrite) against the coil raises L above bare (~1.1-1.4×) and masks the floor -&gt; C9 ≈ 52-77 pF est., 68/82 the likely rungs; same ladder covers all three builds. Final trim always with the full stack (brace + ferrite + shell) installed.</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -3082,57 +3082,63 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>FER1</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="B46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>NFC ferrite backing — flexible sintered ferrite patch pressed against the board back over the antenna; masks the shell floor (kills eddy detune + Q loss), raises coil L</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>WE-FSFS material 364 (13.56 MHz grade), 0.3 mm, cut to 12.2 × 25.8 mm</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>WE-FSFS material 364 (13.56 MHz grade), 0.38 mm overall stack, cut to 12.2 × 25.8 mm</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
         <is>
           <t>60 × 60 × 0.3 mm sheet (yields 4 patches)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="10" t="inlineStr">
         <is>
           <t>Würth Elektronik</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>364006</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="H46" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="I46" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>AUX</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Observed at RS 2026-07-03 (364006 = 60×60×0.3 WE-FSFS); DigiKey carries the WE-FSFS line — confirm size/thickness variant at cart (~$15-20 sheet class at RS/Farnell). Material 364 is Würth’s 13.56 MHz redirection grade per app note ANP022 (metal detune elimination described verbatim). Laser-scored 2×2 mm grid cuts to size; PET face to the board, PSA face into the brace pocket (brace stays removable, ferrite captive). Non-conductive as supplied. Alternates: MARUWA FSF131/FSF151 (µ′ 130–150 @13.56), Fair-Rite flexible sheets.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>ANP022 (Würth app note)</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>(confirm at cart — order by MPN 364006)</t>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>DK page fetched 2026-07-03 (Devin-supplied URL): 732-5049-ND, Active, 51 in stock, tray, $17.43 @ 1, mfr lead 24 wk once depleted — buy with the order. Verbatim: 60.00 × 60.00 mm × 0.015" (0.38 mm) overall, "Rubber, Ferrite Powder, PET Film Non-Conductive, Single Sided" adhesive, −40~85 °C. Pocket depth keys off 0.38 (measure delivered sheet; pocket = measured − 0.05). PET face to board, PSA into brace pocket. Cheaper 60×60 alternates observed on the same page (verify grade/thickness vs datasheet before substituting): Würth 3641014 $4.19, Laird MHLL6060-300 $6.40.</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Worth ferrite sheet .pdf (repo; suggest rename WE-FSFS-364006.pdf)</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>732-5049-ND</t>
         </is>
       </c>
     </row>

--- a/PCB/solar-glow-drh-v3 0-BOM.xlsx
+++ b/PCB/solar-glow-drh-v3 0-BOM.xlsx
@@ -3115,10 +3115,10 @@
           <t>364006</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="10" t="n">
         <v>17.43</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46" s="10" t="n">
         <v>17.43</v>
       </c>
       <c r="J46" s="10" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>DK page fetched 2026-07-03 (Devin-supplied URL): 732-5049-ND, Active, 51 in stock, tray, $17.43 @ 1, mfr lead 24 wk once depleted — buy with the order. Verbatim: 60.00 × 60.00 mm × 0.015" (0.38 mm) overall, "Rubber, Ferrite Powder, PET Film Non-Conductive, Single Sided" adhesive, −40~85 °C. Pocket depth keys off 0.38 (measure delivered sheet; pocket = measured − 0.05). PET face to board, PSA into brace pocket. Cheaper 60×60 alternates observed on the same page (verify grade/thickness vs datasheet before substituting): Würth 3641014 $4.19, Laird MHLL6060-300 $6.40.</t>
+          <t>DK page fetched 2026-07-03: 732-5049-ND, Active, 51 in stock, tray, $17.43 @ 1, mfr lead 24 wk once depleted — buy with the order. Verbatim: 60×60 mm, 0.38 mm overall stack (ferrite ~0.3 + PET + non-conductive single-sided PSA). Pocket depth keys off measured stack − 0.05. PET face to board, PSA into brace pocket. PRIMARY because the machined pocket makes thickness free and shield strength scales with µ′×t_ferrite. Verified alternates (all thinner, same µ′-class material): Würth 3641014 = 732-13935-ND, $4.19, 379 stock, µ′150/µ″3 @13.56 MHz, ferrite 0.1 mm, 0.14 stack (datasheet in repo) — ~1/3 the shield, OR stack 3 layers (~$12.57, ~0.42 stack) to approximate 364006 if its stock dries; Laird MHLL6060-300 = 240-2791-ND, $6.40, 4,778 stock, 0.09 mm overall, µ′ graph-only (datasheet in repo) — thinnest, weakest. DK also lists mid-family 364103/364104/364105 ($7.46/$8.85/$11.18, thicknesses unverified).</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>Worth ferrite sheet .pdf (repo; suggest rename WE-FSFS-364006.pdf)</t>
+          <t>Worth ferrite sheet .pdf + Ferrite layer 2.pdf + Laird ferrite.pdf (repo)</t>
         </is>
       </c>
       <c r="M46" s="10" t="inlineStr">
